--- a/data/trans_bre/DC-Clase-trans_bre.xlsx
+++ b/data/trans_bre/DC-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 11,0</t>
+          <t>-0,32; 11,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 17,11</t>
+          <t>6,57; 17,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 6,38</t>
+          <t>-3,36; 5,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,65; 21,72</t>
+          <t>11,32; 21,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 77,68</t>
+          <t>-2,33; 80,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,16; 294,0</t>
+          <t>67,14; 302,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 71,87</t>
+          <t>-26,47; 67,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,45; 139,57</t>
+          <t>52,0; 136,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 23,53</t>
+          <t>12,56; 24,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 15,2</t>
+          <t>4,49; 15,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 15,99</t>
+          <t>7,02; 16,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 21,58</t>
+          <t>10,4; 21,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,63; 262,31</t>
+          <t>85,14; 264,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,28; 207,72</t>
+          <t>36,14; 206,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,02; 376,78</t>
+          <t>84,94; 426,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,46; 127,71</t>
+          <t>46,55; 130,89</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 18,34</t>
+          <t>2,63; 18,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 17,21</t>
+          <t>5,3; 17,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 23,66</t>
+          <t>9,38; 23,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,46; 43,79</t>
+          <t>18,13; 41,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 97,1</t>
+          <t>9,43; 95,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,36; 171,97</t>
+          <t>39,91; 176,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,49; 312,21</t>
+          <t>90,05; 320,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66,13; 697,85</t>
+          <t>69,72; 631,3</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 12,63</t>
+          <t>4,13; 12,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,42</t>
+          <t>5,46; 12,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,01</t>
+          <t>3,3; 10,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 50,38</t>
+          <t>10,43; 47,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 62,41</t>
+          <t>18,89; 61,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,77; 106,62</t>
+          <t>38,07; 108,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,18; 108,45</t>
+          <t>26,35; 106,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,65; 221,78</t>
+          <t>42,0; 215,01</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,82</t>
+          <t>1,44; 13,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,87; 22,83</t>
+          <t>14,04; 23,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 13,71</t>
+          <t>5,31; 13,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,94; 37,48</t>
+          <t>16,81; 37,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 82,5</t>
+          <t>5,98; 77,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>114,41; 297,98</t>
+          <t>116,63; 309,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,31; 121,57</t>
+          <t>34,95; 119,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,91; 162,68</t>
+          <t>60,87; 162,22</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,42; 28,39</t>
+          <t>22,6; 28,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,43; 25,57</t>
+          <t>18,15; 25,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,51; 19,0</t>
+          <t>13,71; 19,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,76; 31,66</t>
+          <t>17,04; 31,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>536,74; 2698,98</t>
+          <t>522,86; 2738,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>289,98; 1712,92</t>
+          <t>293,54; 1777,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>462,48; 5163,42</t>
+          <t>458,07; 5547,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94,32; 534,27</t>
+          <t>84,98; 515,52</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,29</t>
+          <t>8,48; 12,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,67; 15,29</t>
+          <t>11,61; 15,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,58</t>
+          <t>7,18; 10,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,88; 33,96</t>
+          <t>17,36; 32,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,72; 74,22</t>
+          <t>45,44; 74,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>103,39; 157,25</t>
+          <t>102,3; 159,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,99; 121,38</t>
+          <t>68,3; 120,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81,54; 188,31</t>
+          <t>79,7; 187,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DC-Clase-trans_bre.xlsx
+++ b/data/trans_bre/DC-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>16,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 11,06</t>
+          <t>-0,09; 11,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 17,02</t>
+          <t>6,48; 17,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,94</t>
+          <t>-3,8; 5,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,32; 21,34</t>
+          <t>11,56; 21,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 80,19</t>
+          <t>-1,42; 79,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,14; 302,43</t>
+          <t>59,43; 257,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 67,88</t>
+          <t>-28,06; 67,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,0; 136,38</t>
+          <t>55,23; 133,79</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,06</t>
+          <t>17,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 24,2</t>
+          <t>12,18; 23,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 15,11</t>
+          <t>4,33; 14,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 16,31</t>
+          <t>6,32; 15,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,4; 21,77</t>
+          <t>12,13; 22,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,14; 264,67</t>
+          <t>87,54; 266,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,14; 206,9</t>
+          <t>36,49; 201,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,94; 426,97</t>
+          <t>71,87; 399,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,55; 130,89</t>
+          <t>54,76; 138,8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29,04</t>
+          <t>20,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>183,38%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 18,2</t>
+          <t>2,27; 19,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 17,08</t>
+          <t>5,62; 17,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 23,7</t>
+          <t>9,25; 23,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 41,82</t>
+          <t>13,31; 27,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 95,24</t>
+          <t>9,15; 103,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,91; 176,72</t>
+          <t>44,69; 178,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,05; 320,13</t>
+          <t>87,19; 314,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,72; 631,3</t>
+          <t>48,39; 126,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,36</t>
+          <t>13,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>104,86%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,56</t>
+          <t>4,28; 12,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 12,7</t>
+          <t>5,41; 13,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,11</t>
+          <t>3,6; 9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 47,7</t>
+          <t>9,04; 16,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 61,88</t>
+          <t>18,46; 60,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,07; 108,95</t>
+          <t>37,03; 110,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,35; 106,27</t>
+          <t>31,33; 106,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,0; 215,01</t>
+          <t>35,44; 77,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,05</t>
+          <t>21,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,01</t>
+          <t>2,29; 13,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 23,19</t>
+          <t>14,48; 22,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 13,56</t>
+          <t>5,45; 13,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,81; 37,21</t>
+          <t>17,2; 26,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 77,15</t>
+          <t>9,84; 79,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>116,63; 309,64</t>
+          <t>125,36; 307,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,95; 119,92</t>
+          <t>34,79; 122,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,87; 162,22</t>
+          <t>62,88; 126,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,68</t>
+          <t>25,21</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>237,66%</t>
+          <t>232,76%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,6; 28,28</t>
+          <t>22,34; 27,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,15; 25,6</t>
+          <t>18,57; 26,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,71; 19,27</t>
+          <t>13,7; 19,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,04; 31,48</t>
+          <t>16,66; 30,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>522,86; 2738,92</t>
+          <t>536,42; 2806,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>293,54; 1777,17</t>
+          <t>294,41; 1980,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>458,07; 5547,57</t>
+          <t>468,43; 5494,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,98; 515,52</t>
+          <t>87,91; 482,91</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,92</t>
+          <t>17,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>113,79%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,43</t>
+          <t>8,37; 12,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,34</t>
+          <t>11,62; 15,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 10,6</t>
+          <t>7,07; 10,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,36; 32,92</t>
+          <t>15,5; 19,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,44; 74,39</t>
+          <t>45,3; 74,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>102,3; 159,79</t>
+          <t>105,37; 162,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,3; 120,01</t>
+          <t>67,37; 118,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79,7; 187,8</t>
+          <t>68,68; 96,92</t>
         </is>
       </c>
     </row>
